--- a/PLAFT/Desarrollo/Minorista_regulado/Documentacion/concialia_pilotos.xlsx
+++ b/PLAFT/Desarrollo/Minorista_regulado/Documentacion/concialia_pilotos.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/PLAFT/Desarrollo/Minorista_regulado/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11B4E0EC-BE97-4283-A8F2-AED132A1E31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_641C90093B1C1D5D51946A1BD12EC7040389ED2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" xr2:uid="{7A996F73-7E09-400D-B267-F98365B683CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,6 +41,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
+    <t>ord envio</t>
+  </si>
+  <si>
     <t>cod_cli_piloto</t>
   </si>
   <si>
@@ -50,10 +53,7 @@
     <t>prob_piloto</t>
   </si>
   <si>
-    <t>rank_modelo_dentro_piloto</t>
-  </si>
-  <si>
-    <t>prob</t>
+    <t>prob_actual</t>
   </si>
   <si>
     <t>dif_prob</t>
@@ -63,7 +63,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -144,6 +144,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,33 +479,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4669A0E4-CDA0-4991-85AF-A668BD46836D}">
-  <dimension ref="A1:G185"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="5" max="5" width="11.54296875" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I185"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>120</v>
       </c>
@@ -518,16 +516,13 @@
         <v>0.99727600000000005</v>
       </c>
       <c r="E2" s="2">
-        <v>23</v>
+        <v>0.99611400000000005</v>
       </c>
       <c r="F2" s="2">
-        <v>0.99611400000000005</v>
-      </c>
-      <c r="G2" s="2">
         <v>-1.1620000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>121</v>
       </c>
@@ -541,16 +536,13 @@
         <v>0.99700699999999998</v>
       </c>
       <c r="E3" s="2">
-        <v>38</v>
+        <v>0.99548099999999995</v>
       </c>
       <c r="F3" s="2">
-        <v>0.99548099999999995</v>
-      </c>
-      <c r="G3" s="2">
         <v>-1.526E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>122</v>
       </c>
@@ -564,16 +556,13 @@
         <v>0.99674600000000002</v>
       </c>
       <c r="E4" s="2">
-        <v>13</v>
+        <v>0.99709999999999999</v>
       </c>
       <c r="F4" s="2">
-        <v>0.99709999999999999</v>
-      </c>
-      <c r="G4" s="2">
         <v>3.5399999999999999E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>123</v>
       </c>
@@ -587,16 +576,13 @@
         <v>0.99666100000000002</v>
       </c>
       <c r="E5" s="2">
-        <v>12</v>
+        <v>0.99710100000000002</v>
       </c>
       <c r="F5" s="2">
-        <v>0.99710100000000002</v>
-      </c>
-      <c r="G5" s="2">
         <v>4.4000000000000002E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>124</v>
       </c>
@@ -610,16 +596,13 @@
         <v>0.99664299999999995</v>
       </c>
       <c r="E6" s="2">
-        <v>47</v>
+        <v>0.99488500000000002</v>
       </c>
       <c r="F6" s="2">
-        <v>0.99488500000000002</v>
-      </c>
-      <c r="G6" s="2">
         <v>-1.7570000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
         <v>125</v>
       </c>
@@ -633,16 +616,13 @@
         <v>0.99661500000000003</v>
       </c>
       <c r="E7" s="2">
-        <v>16</v>
+        <v>0.996892</v>
       </c>
       <c r="F7" s="2">
-        <v>0.996892</v>
-      </c>
-      <c r="G7" s="2">
         <v>2.7700000000000001E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
         <v>126</v>
       </c>
@@ -656,16 +636,13 @@
         <v>0.996533</v>
       </c>
       <c r="E8" s="2">
-        <v>10</v>
+        <v>0.99718499999999999</v>
       </c>
       <c r="F8" s="2">
-        <v>0.99718499999999999</v>
-      </c>
-      <c r="G8" s="2">
         <v>6.5200000000000002E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
         <v>127</v>
       </c>
@@ -679,16 +656,13 @@
         <v>0.99644600000000005</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>0.99450400000000005</v>
       </c>
       <c r="F9" s="2">
-        <v>0.99450400000000005</v>
-      </c>
-      <c r="G9" s="2">
         <v>-1.9419999999999999E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
         <v>128</v>
       </c>
@@ -702,16 +676,13 @@
         <v>0.99640200000000001</v>
       </c>
       <c r="E10" s="2">
-        <v>19</v>
+        <v>0.99666200000000005</v>
       </c>
       <c r="F10" s="2">
-        <v>0.99666200000000005</v>
-      </c>
-      <c r="G10" s="2">
         <v>2.5999999999999998E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
         <v>129</v>
       </c>
@@ -725,16 +696,13 @@
         <v>0.99622599999999994</v>
       </c>
       <c r="E11" s="2">
-        <v>25</v>
+        <v>0.99583999999999995</v>
       </c>
       <c r="F11" s="2">
-        <v>0.99583999999999995</v>
-      </c>
-      <c r="G11" s="2">
         <v>-3.86E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
         <v>130</v>
       </c>
@@ -748,16 +716,13 @@
         <v>0.99618899999999999</v>
       </c>
       <c r="E12" s="2">
-        <v>36</v>
+        <v>0.99549799999999999</v>
       </c>
       <c r="F12" s="2">
-        <v>0.99549799999999999</v>
-      </c>
-      <c r="G12" s="2">
         <v>-6.9099999999999999E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6">
       <c r="A13" s="2">
         <v>131</v>
       </c>
@@ -771,16 +736,13 @@
         <v>0.99614199999999997</v>
       </c>
       <c r="E13" s="2">
-        <v>128</v>
+        <v>0.98768100000000003</v>
       </c>
       <c r="F13" s="2">
-        <v>0.98768100000000003</v>
-      </c>
-      <c r="G13" s="2">
         <v>-8.4600000000000005E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6">
       <c r="A14" s="2">
         <v>132</v>
       </c>
@@ -794,16 +756,13 @@
         <v>0.99601799999999996</v>
       </c>
       <c r="E14" s="2">
-        <v>20</v>
+        <v>0.99665599999999999</v>
       </c>
       <c r="F14" s="2">
-        <v>0.99665599999999999</v>
-      </c>
-      <c r="G14" s="2">
         <v>6.38E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6">
       <c r="A15" s="2">
         <v>133</v>
       </c>
@@ -817,16 +776,13 @@
         <v>0.99593699999999996</v>
       </c>
       <c r="E15" s="2">
-        <v>79</v>
+        <v>0.99331499999999995</v>
       </c>
       <c r="F15" s="2">
-        <v>0.99331499999999995</v>
-      </c>
-      <c r="G15" s="2">
         <v>-2.6229999999999999E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6">
       <c r="A16" s="2">
         <v>134</v>
       </c>
@@ -840,16 +796,13 @@
         <v>0.99590699999999999</v>
       </c>
       <c r="E16" s="2">
-        <v>55</v>
+        <v>0.99451000000000001</v>
       </c>
       <c r="F16" s="2">
-        <v>0.99451000000000001</v>
-      </c>
-      <c r="G16" s="2">
         <v>-1.3979999999999999E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="A17" s="2">
         <v>135</v>
       </c>
@@ -863,16 +816,13 @@
         <v>0.99578900000000004</v>
       </c>
       <c r="E17" s="2">
-        <v>50</v>
+        <v>0.99472899999999997</v>
       </c>
       <c r="F17" s="2">
-        <v>0.99472899999999997</v>
-      </c>
-      <c r="G17" s="2">
         <v>-1.06E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="A18" s="2">
         <v>136</v>
       </c>
@@ -886,16 +836,13 @@
         <v>0.99576200000000004</v>
       </c>
       <c r="E18" s="2">
-        <v>2</v>
+        <v>0.99849200000000005</v>
       </c>
       <c r="F18" s="2">
-        <v>0.99849200000000005</v>
-      </c>
-      <c r="G18" s="2">
         <v>2.7299999999999998E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="A19" s="2">
         <v>137</v>
       </c>
@@ -909,16 +856,13 @@
         <v>0.99575599999999997</v>
       </c>
       <c r="E19" s="2">
-        <v>81</v>
+        <v>0.993147</v>
       </c>
       <c r="F19" s="2">
-        <v>0.993147</v>
-      </c>
-      <c r="G19" s="2">
         <v>-2.6090000000000002E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="A20" s="2">
         <v>138</v>
       </c>
@@ -932,16 +876,13 @@
         <v>0.99569099999999999</v>
       </c>
       <c r="E20" s="2">
-        <v>15</v>
+        <v>0.99690199999999995</v>
       </c>
       <c r="F20" s="2">
-        <v>0.99690199999999995</v>
-      </c>
-      <c r="G20" s="2">
         <v>1.2110000000000001E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="A21" s="2">
         <v>139</v>
       </c>
@@ -955,16 +896,13 @@
         <v>0.99568100000000004</v>
       </c>
       <c r="E21" s="2">
-        <v>11</v>
+        <v>0.99717500000000003</v>
       </c>
       <c r="F21" s="2">
-        <v>0.99717500000000003</v>
-      </c>
-      <c r="G21" s="2">
         <v>1.4940000000000001E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="A22" s="2">
         <v>140</v>
       </c>
@@ -978,16 +916,13 @@
         <v>0.99566399999999999</v>
       </c>
       <c r="E22" s="2">
-        <v>35</v>
+        <v>0.99551699999999999</v>
       </c>
       <c r="F22" s="2">
-        <v>0.99551699999999999</v>
-      </c>
-      <c r="G22" s="2">
         <v>-1.47E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6">
       <c r="A23" s="2">
         <v>141</v>
       </c>
@@ -1001,16 +936,13 @@
         <v>0.995618</v>
       </c>
       <c r="E23" s="2">
-        <v>43</v>
+        <v>0.99526300000000001</v>
       </c>
       <c r="F23" s="2">
-        <v>0.99526300000000001</v>
-      </c>
-      <c r="G23" s="2">
         <v>-3.5500000000000001E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6">
       <c r="A24" s="2">
         <v>142</v>
       </c>
@@ -1024,16 +956,13 @@
         <v>0.99556599999999995</v>
       </c>
       <c r="E24" s="2">
-        <v>78</v>
+        <v>0.99331599999999998</v>
       </c>
       <c r="F24" s="2">
-        <v>0.99331599999999998</v>
-      </c>
-      <c r="G24" s="2">
         <v>-2.2499999999999998E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6">
       <c r="A25" s="2">
         <v>143</v>
       </c>
@@ -1047,16 +976,13 @@
         <v>0.99550700000000003</v>
       </c>
       <c r="E25" s="2">
-        <v>93</v>
+        <v>0.99221700000000002</v>
       </c>
       <c r="F25" s="2">
-        <v>0.99221700000000002</v>
-      </c>
-      <c r="G25" s="2">
         <v>-3.2910000000000001E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6">
       <c r="A26" s="2">
         <v>144</v>
       </c>
@@ -1070,16 +996,13 @@
         <v>0.99529900000000004</v>
       </c>
       <c r="E26" s="2">
-        <v>14</v>
+        <v>0.997089</v>
       </c>
       <c r="F26" s="2">
-        <v>0.997089</v>
-      </c>
-      <c r="G26" s="2">
         <v>1.7899999999999999E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6">
       <c r="A27" s="2">
         <v>145</v>
       </c>
@@ -1093,16 +1016,13 @@
         <v>0.99520799999999998</v>
       </c>
       <c r="E27" s="2">
-        <v>5</v>
+        <v>0.99817400000000001</v>
       </c>
       <c r="F27" s="2">
-        <v>0.99817400000000001</v>
-      </c>
-      <c r="G27" s="2">
         <v>2.9659999999999999E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6">
       <c r="A28" s="2">
         <v>146</v>
       </c>
@@ -1116,16 +1036,13 @@
         <v>0.99519800000000003</v>
       </c>
       <c r="E28" s="2">
-        <v>89</v>
+        <v>0.99235600000000002</v>
       </c>
       <c r="F28" s="2">
-        <v>0.99235600000000002</v>
-      </c>
-      <c r="G28" s="2">
         <v>-2.8410000000000002E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6">
       <c r="A29" s="2">
         <v>147</v>
       </c>
@@ -1139,16 +1056,13 @@
         <v>0.99516499999999997</v>
       </c>
       <c r="E29" s="2">
-        <v>83</v>
+        <v>0.993066</v>
       </c>
       <c r="F29" s="2">
-        <v>0.993066</v>
-      </c>
-      <c r="G29" s="2">
         <v>-2.0990000000000002E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6">
       <c r="A30" s="2">
         <v>148</v>
       </c>
@@ -1162,16 +1076,13 @@
         <v>0.99514400000000003</v>
       </c>
       <c r="E30" s="2">
-        <v>1</v>
+        <v>0.99887899999999996</v>
       </c>
       <c r="F30" s="2">
-        <v>0.99887899999999996</v>
-      </c>
-      <c r="G30" s="2">
         <v>3.735E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="A31" s="2">
         <v>149</v>
       </c>
@@ -1185,16 +1096,13 @@
         <v>0.99510900000000002</v>
       </c>
       <c r="E31" s="2">
-        <v>52</v>
+        <v>0.99459799999999998</v>
       </c>
       <c r="F31" s="2">
-        <v>0.99459799999999998</v>
-      </c>
-      <c r="G31" s="2">
         <v>-5.1099999999999995E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6">
       <c r="A32" s="3">
         <v>150</v>
       </c>
@@ -1208,16 +1116,13 @@
         <v>0.99509300000000001</v>
       </c>
       <c r="E32" s="3">
-        <v>178</v>
-      </c>
-      <c r="F32" s="3">
         <v>0.583673</v>
       </c>
-      <c r="G32" s="2">
+      <c r="F32" s="2">
         <v>-0.41142000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9">
       <c r="A33" s="2">
         <v>151</v>
       </c>
@@ -1231,16 +1136,13 @@
         <v>0.99501300000000004</v>
       </c>
       <c r="E33" s="2">
-        <v>63</v>
+        <v>0.99412900000000004</v>
       </c>
       <c r="F33" s="2">
-        <v>0.99412900000000004</v>
-      </c>
-      <c r="G33" s="2">
         <v>-8.8400000000000002E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9">
       <c r="A34" s="2">
         <v>152</v>
       </c>
@@ -1254,16 +1156,13 @@
         <v>0.99500299999999997</v>
       </c>
       <c r="E34" s="2">
-        <v>57</v>
+        <v>0.99449399999999999</v>
       </c>
       <c r="F34" s="2">
-        <v>0.99449399999999999</v>
-      </c>
-      <c r="G34" s="2">
         <v>-5.0900000000000001E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9">
       <c r="A35" s="2">
         <v>153</v>
       </c>
@@ -1277,16 +1176,13 @@
         <v>0.99496899999999999</v>
       </c>
       <c r="E35" s="2">
-        <v>32</v>
+        <v>0.99563699999999999</v>
       </c>
       <c r="F35" s="2">
-        <v>0.99563699999999999</v>
-      </c>
-      <c r="G35" s="2">
         <v>6.6799999999999997E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9">
       <c r="A36" s="2">
         <v>154</v>
       </c>
@@ -1300,16 +1196,13 @@
         <v>0.994923</v>
       </c>
       <c r="E36" s="2">
-        <v>8</v>
+        <v>0.99805600000000005</v>
       </c>
       <c r="F36" s="2">
-        <v>0.99805600000000005</v>
-      </c>
-      <c r="G36" s="2">
         <v>3.1340000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9">
       <c r="A37" s="2">
         <v>155</v>
       </c>
@@ -1323,16 +1216,13 @@
         <v>0.99476500000000001</v>
       </c>
       <c r="E37" s="2">
-        <v>45</v>
+        <v>0.99516899999999997</v>
       </c>
       <c r="F37" s="2">
-        <v>0.99516899999999997</v>
-      </c>
-      <c r="G37" s="2">
         <v>4.0400000000000001E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9">
       <c r="A38" s="3">
         <v>156</v>
       </c>
@@ -1346,16 +1236,13 @@
         <v>0.99466100000000002</v>
       </c>
       <c r="E38" s="3">
-        <v>183</v>
-      </c>
-      <c r="F38" s="3">
         <v>0.252419</v>
       </c>
-      <c r="G38" s="2">
+      <c r="F38" s="2">
         <v>-0.74224199999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9">
       <c r="A39" s="2">
         <v>157</v>
       </c>
@@ -1369,16 +1256,13 @@
         <v>0.994614</v>
       </c>
       <c r="E39" s="2">
-        <v>64</v>
+        <v>0.99411899999999997</v>
       </c>
       <c r="F39" s="2">
-        <v>0.99411899999999997</v>
-      </c>
-      <c r="G39" s="2">
         <v>-4.95E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9">
       <c r="A40" s="2">
         <v>158</v>
       </c>
@@ -1392,16 +1276,13 @@
         <v>0.99459200000000003</v>
       </c>
       <c r="E40" s="2">
-        <v>24</v>
+        <v>0.99586600000000003</v>
       </c>
       <c r="F40" s="2">
-        <v>0.99586600000000003</v>
-      </c>
-      <c r="G40" s="2">
         <v>1.274E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9">
       <c r="A41" s="2">
         <v>159</v>
       </c>
@@ -1415,16 +1296,13 @@
         <v>0.99457200000000001</v>
       </c>
       <c r="E41" s="2">
-        <v>22</v>
+        <v>0.99625300000000006</v>
       </c>
       <c r="F41" s="2">
-        <v>0.99625300000000006</v>
-      </c>
-      <c r="G41" s="2">
         <v>1.681E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9">
       <c r="A42" s="2">
         <v>160</v>
       </c>
@@ -1438,16 +1316,13 @@
         <v>0.99456800000000001</v>
       </c>
       <c r="E42" s="2">
-        <v>18</v>
+        <v>0.99667099999999997</v>
       </c>
       <c r="F42" s="2">
-        <v>0.99667099999999997</v>
-      </c>
-      <c r="G42" s="2">
         <v>2.1029999999999998E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9">
       <c r="A43" s="2">
         <v>161</v>
       </c>
@@ -1461,39 +1336,33 @@
         <v>0.99456299999999997</v>
       </c>
       <c r="E43" s="2">
-        <v>39</v>
+        <v>0.99544100000000002</v>
       </c>
       <c r="F43" s="2">
-        <v>0.99544100000000002</v>
-      </c>
-      <c r="G43" s="2">
         <v>8.7900000000000001E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="4">
+    <row r="44" spans="1:9">
+      <c r="A44" s="2">
         <v>162</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="2">
         <v>22109298</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="2">
         <v>43</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="2">
         <v>0.99451500000000004</v>
       </c>
-      <c r="E44" s="4">
-        <v>150</v>
-      </c>
-      <c r="F44" s="4">
+      <c r="E44" s="2">
         <v>0.97978799999999999</v>
       </c>
-      <c r="G44" s="2">
+      <c r="F44" s="2">
         <v>-1.4728E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9">
       <c r="A45" s="2">
         <v>163</v>
       </c>
@@ -1507,16 +1376,13 @@
         <v>0.99448999999999999</v>
       </c>
       <c r="E45" s="2">
-        <v>74</v>
+        <v>0.99356900000000004</v>
       </c>
       <c r="F45" s="2">
-        <v>0.99356900000000004</v>
-      </c>
-      <c r="G45" s="2">
         <v>-9.2000000000000003E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9">
       <c r="A46" s="2">
         <v>164</v>
       </c>
@@ -1530,16 +1396,17 @@
         <v>0.994452</v>
       </c>
       <c r="E46" s="2">
-        <v>92</v>
+        <v>0.99223099999999997</v>
       </c>
       <c r="F46" s="2">
-        <v>0.99223099999999997</v>
-      </c>
-      <c r="G46" s="2">
         <v>-2.2209999999999999E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I46" s="5">
+        <f>7/188</f>
+        <v>3.7234042553191488E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="2">
         <v>165</v>
       </c>
@@ -1553,16 +1420,13 @@
         <v>0.99445099999999997</v>
       </c>
       <c r="E47" s="2">
-        <v>69</v>
+        <v>0.99379399999999996</v>
       </c>
       <c r="F47" s="2">
-        <v>0.99379399999999996</v>
-      </c>
-      <c r="G47" s="2">
         <v>-6.5700000000000003E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9">
       <c r="A48" s="2">
         <v>166</v>
       </c>
@@ -1576,16 +1440,13 @@
         <v>0.99444699999999997</v>
       </c>
       <c r="E48" s="2">
-        <v>40</v>
+        <v>0.99536999999999998</v>
       </c>
       <c r="F48" s="2">
-        <v>0.99536999999999998</v>
-      </c>
-      <c r="G48" s="2">
         <v>9.2299999999999999E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6">
       <c r="A49" s="2">
         <v>167</v>
       </c>
@@ -1599,16 +1460,13 @@
         <v>0.99440799999999996</v>
       </c>
       <c r="E49" s="2">
-        <v>7</v>
+        <v>0.99808300000000005</v>
       </c>
       <c r="F49" s="2">
-        <v>0.99808300000000005</v>
-      </c>
-      <c r="G49" s="2">
         <v>3.6740000000000002E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6">
       <c r="A50" s="2">
         <v>168</v>
       </c>
@@ -1622,16 +1480,13 @@
         <v>0.99437900000000001</v>
       </c>
       <c r="E50" s="2">
-        <v>42</v>
+        <v>0.995286</v>
       </c>
       <c r="F50" s="2">
-        <v>0.995286</v>
-      </c>
-      <c r="G50" s="2">
         <v>9.0700000000000004E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="A51" s="2">
         <v>169</v>
       </c>
@@ -1645,16 +1500,13 @@
         <v>0.99434500000000003</v>
       </c>
       <c r="E51" s="2">
-        <v>41</v>
+        <v>0.99535300000000004</v>
       </c>
       <c r="F51" s="2">
-        <v>0.99535300000000004</v>
-      </c>
-      <c r="G51" s="2">
         <v>1.008E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6">
       <c r="A52" s="2">
         <v>170</v>
       </c>
@@ -1668,16 +1520,13 @@
         <v>0.99419100000000005</v>
       </c>
       <c r="E52" s="2">
-        <v>4</v>
+        <v>0.99822100000000002</v>
       </c>
       <c r="F52" s="2">
-        <v>0.99822100000000002</v>
-      </c>
-      <c r="G52" s="2">
         <v>4.0299999999999997E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6">
       <c r="A53" s="2">
         <v>171</v>
       </c>
@@ -1691,16 +1540,13 @@
         <v>0.99415100000000001</v>
       </c>
       <c r="E53" s="2">
-        <v>99</v>
+        <v>0.991232</v>
       </c>
       <c r="F53" s="2">
-        <v>0.991232</v>
-      </c>
-      <c r="G53" s="2">
         <v>-2.9190000000000002E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6">
       <c r="A54" s="2">
         <v>172</v>
       </c>
@@ -1714,16 +1560,13 @@
         <v>0.99391399999999996</v>
       </c>
       <c r="E54" s="2">
-        <v>27</v>
+        <v>0.99575899999999995</v>
       </c>
       <c r="F54" s="2">
-        <v>0.99575899999999995</v>
-      </c>
-      <c r="G54" s="2">
         <v>1.8450000000000001E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6">
       <c r="A55" s="2">
         <v>173</v>
       </c>
@@ -1737,16 +1580,13 @@
         <v>0.99387899999999996</v>
       </c>
       <c r="E55" s="2">
-        <v>86</v>
+        <v>0.99282400000000004</v>
       </c>
       <c r="F55" s="2">
-        <v>0.99282400000000004</v>
-      </c>
-      <c r="G55" s="2">
         <v>-1.0549999999999999E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6">
       <c r="A56" s="2">
         <v>174</v>
       </c>
@@ -1760,16 +1600,13 @@
         <v>0.99373</v>
       </c>
       <c r="E56" s="2">
-        <v>77</v>
+        <v>0.99336599999999997</v>
       </c>
       <c r="F56" s="2">
-        <v>0.99336599999999997</v>
-      </c>
-      <c r="G56" s="2">
         <v>-3.6400000000000001E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="A57" s="2">
         <v>175</v>
       </c>
@@ -1783,16 +1620,13 @@
         <v>0.99368599999999996</v>
       </c>
       <c r="E57" s="2">
-        <v>17</v>
+        <v>0.99686200000000003</v>
       </c>
       <c r="F57" s="2">
-        <v>0.99686200000000003</v>
-      </c>
-      <c r="G57" s="2">
         <v>3.176E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="A58" s="2">
         <v>176</v>
       </c>
@@ -1806,16 +1640,13 @@
         <v>0.99363299999999999</v>
       </c>
       <c r="E58" s="2">
-        <v>6</v>
+        <v>0.99816000000000005</v>
       </c>
       <c r="F58" s="2">
-        <v>0.99816000000000005</v>
-      </c>
-      <c r="G58" s="2">
         <v>4.5269999999999998E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="A59" s="2">
         <v>177</v>
       </c>
@@ -1829,16 +1660,13 @@
         <v>0.99352099999999999</v>
       </c>
       <c r="E59" s="2">
-        <v>75</v>
+        <v>0.993502</v>
       </c>
       <c r="F59" s="2">
-        <v>0.993502</v>
-      </c>
-      <c r="G59" s="2">
         <v>-1.8E-5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6">
       <c r="A60" s="2">
         <v>178</v>
       </c>
@@ -1852,16 +1680,13 @@
         <v>0.99350799999999995</v>
       </c>
       <c r="E60" s="2">
-        <v>141</v>
+        <v>0.98491899999999999</v>
       </c>
       <c r="F60" s="2">
-        <v>0.98491899999999999</v>
-      </c>
-      <c r="G60" s="2">
         <v>-8.5889999999999994E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6">
       <c r="A61" s="2">
         <v>179</v>
       </c>
@@ -1875,16 +1700,13 @@
         <v>0.993479</v>
       </c>
       <c r="E61" s="2">
-        <v>9</v>
+        <v>0.99789700000000003</v>
       </c>
       <c r="F61" s="2">
-        <v>0.99789700000000003</v>
-      </c>
-      <c r="G61" s="2">
         <v>4.4180000000000001E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="2">
         <v>180</v>
       </c>
@@ -1898,16 +1720,13 @@
         <v>0.99341900000000005</v>
       </c>
       <c r="E62" s="2">
-        <v>30</v>
+        <v>0.99565599999999999</v>
       </c>
       <c r="F62" s="2">
-        <v>0.99565599999999999</v>
-      </c>
-      <c r="G62" s="2">
         <v>2.2369999999999998E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6">
       <c r="A63" s="2">
         <v>181</v>
       </c>
@@ -1921,16 +1740,13 @@
         <v>0.99339</v>
       </c>
       <c r="E63" s="2">
-        <v>53</v>
+        <v>0.99458899999999995</v>
       </c>
       <c r="F63" s="2">
-        <v>0.99458899999999995</v>
-      </c>
-      <c r="G63" s="2">
         <v>1.199E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6">
       <c r="A64" s="2">
         <v>182</v>
       </c>
@@ -1944,16 +1760,13 @@
         <v>0.99327100000000002</v>
       </c>
       <c r="E64" s="2">
-        <v>87</v>
+        <v>0.99258400000000002</v>
       </c>
       <c r="F64" s="2">
-        <v>0.99258400000000002</v>
-      </c>
-      <c r="G64" s="2">
         <v>-6.8599999999999998E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>183</v>
       </c>
@@ -1967,16 +1780,13 @@
         <v>0.99322500000000002</v>
       </c>
       <c r="E65" s="1">
-        <v>102</v>
+        <v>0.99111000000000005</v>
       </c>
       <c r="F65" s="1">
-        <v>0.99111000000000005</v>
-      </c>
-      <c r="G65" s="1">
         <v>-2.114E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6">
       <c r="A66" s="2">
         <v>0</v>
       </c>
@@ -1990,16 +1800,13 @@
         <v>0.99293500000000001</v>
       </c>
       <c r="E66" s="2">
-        <v>62</v>
+        <v>0.99416099999999996</v>
       </c>
       <c r="F66" s="2">
-        <v>0.99416099999999996</v>
-      </c>
-      <c r="G66" s="2">
         <v>1.225E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6">
       <c r="A67" s="2">
         <v>1</v>
       </c>
@@ -2013,16 +1820,13 @@
         <v>0.99292599999999998</v>
       </c>
       <c r="E67" s="2">
-        <v>97</v>
+        <v>0.99168900000000004</v>
       </c>
       <c r="F67" s="2">
-        <v>0.99168900000000004</v>
-      </c>
-      <c r="G67" s="2">
         <v>-1.237E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="A68" s="2">
         <v>2</v>
       </c>
@@ -2036,16 +1840,13 @@
         <v>0.99292400000000003</v>
       </c>
       <c r="E68" s="2">
-        <v>96</v>
+        <v>0.99182899999999996</v>
       </c>
       <c r="F68" s="2">
-        <v>0.99182899999999996</v>
-      </c>
-      <c r="G68" s="2">
         <v>-1.0950000000000001E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6">
       <c r="A69" s="2">
         <v>3</v>
       </c>
@@ -2059,16 +1860,13 @@
         <v>0.992869</v>
       </c>
       <c r="E69" s="2">
-        <v>109</v>
+        <v>0.99043499999999995</v>
       </c>
       <c r="F69" s="2">
-        <v>0.99043499999999995</v>
-      </c>
-      <c r="G69" s="2">
         <v>-2.434E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6">
       <c r="A70" s="2">
         <v>4</v>
       </c>
@@ -2082,16 +1880,13 @@
         <v>0.992842</v>
       </c>
       <c r="E70" s="2">
-        <v>90</v>
+        <v>0.99234100000000003</v>
       </c>
       <c r="F70" s="2">
-        <v>0.99234100000000003</v>
-      </c>
-      <c r="G70" s="2">
         <v>-5.0100000000000003E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="A71" s="2">
         <v>5</v>
       </c>
@@ -2105,16 +1900,13 @@
         <v>0.992784</v>
       </c>
       <c r="E71" s="2">
-        <v>26</v>
+        <v>0.99577000000000004</v>
       </c>
       <c r="F71" s="2">
-        <v>0.99577000000000004</v>
-      </c>
-      <c r="G71" s="2">
         <v>2.9859999999999999E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="A72" s="2">
         <v>6</v>
       </c>
@@ -2128,16 +1920,13 @@
         <v>0.99266699999999997</v>
       </c>
       <c r="E72" s="2">
-        <v>49</v>
+        <v>0.99473400000000001</v>
       </c>
       <c r="F72" s="2">
-        <v>0.99473400000000001</v>
-      </c>
-      <c r="G72" s="2">
         <v>2.0669999999999998E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6">
       <c r="A73" s="2">
         <v>7</v>
       </c>
@@ -2151,16 +1940,13 @@
         <v>0.99257300000000004</v>
       </c>
       <c r="E73" s="2">
-        <v>107</v>
+        <v>0.99078500000000003</v>
       </c>
       <c r="F73" s="2">
-        <v>0.99078500000000003</v>
-      </c>
-      <c r="G73" s="2">
         <v>-1.7880000000000001E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6">
       <c r="A74" s="2">
         <v>8</v>
       </c>
@@ -2174,16 +1960,13 @@
         <v>0.99246900000000005</v>
       </c>
       <c r="E74" s="2">
-        <v>105</v>
+        <v>0.99090999999999996</v>
       </c>
       <c r="F74" s="2">
-        <v>0.99090999999999996</v>
-      </c>
-      <c r="G74" s="2">
         <v>-1.5590000000000001E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6">
       <c r="A75" s="2">
         <v>9</v>
       </c>
@@ -2197,16 +1980,13 @@
         <v>0.99245799999999995</v>
       </c>
       <c r="E75" s="2">
-        <v>61</v>
+        <v>0.99417100000000003</v>
       </c>
       <c r="F75" s="2">
-        <v>0.99417100000000003</v>
-      </c>
-      <c r="G75" s="2">
         <v>1.7129999999999999E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6">
       <c r="A76" s="3">
         <v>10</v>
       </c>
@@ -2220,16 +2000,13 @@
         <v>0.99223799999999995</v>
       </c>
       <c r="E76" s="3">
-        <v>179</v>
-      </c>
-      <c r="F76" s="3">
         <v>0.41164699999999999</v>
       </c>
-      <c r="G76" s="2">
+      <c r="F76" s="2">
         <v>-0.58059099999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="A77" s="4">
         <v>11</v>
       </c>
@@ -2243,16 +2020,13 @@
         <v>0.99220600000000003</v>
       </c>
       <c r="E77" s="4">
-        <v>176</v>
-      </c>
-      <c r="F77" s="4">
         <v>0.88359200000000004</v>
       </c>
-      <c r="G77" s="2">
+      <c r="F77" s="2">
         <v>-0.108614</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6">
       <c r="A78" s="2">
         <v>12</v>
       </c>
@@ -2266,16 +2040,13 @@
         <v>0.99217500000000003</v>
       </c>
       <c r="E78" s="2">
-        <v>82</v>
+        <v>0.99311700000000003</v>
       </c>
       <c r="F78" s="2">
-        <v>0.99311700000000003</v>
-      </c>
-      <c r="G78" s="2">
         <v>9.4200000000000002E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6">
       <c r="A79" s="2">
         <v>13</v>
       </c>
@@ -2289,16 +2060,13 @@
         <v>0.992116</v>
       </c>
       <c r="E79" s="2">
-        <v>145</v>
+        <v>0.98314900000000005</v>
       </c>
       <c r="F79" s="2">
-        <v>0.98314900000000005</v>
-      </c>
-      <c r="G79" s="2">
         <v>-8.9669999999999993E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="2">
         <v>14</v>
       </c>
@@ -2312,16 +2080,13 @@
         <v>0.99205100000000002</v>
       </c>
       <c r="E80" s="2">
-        <v>73</v>
+        <v>0.99357700000000004</v>
       </c>
       <c r="F80" s="2">
-        <v>0.99357700000000004</v>
-      </c>
-      <c r="G80" s="2">
         <v>1.526E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6">
       <c r="A81" s="2">
         <v>15</v>
       </c>
@@ -2335,16 +2100,13 @@
         <v>0.99178299999999997</v>
       </c>
       <c r="E81" s="2">
-        <v>101</v>
+        <v>0.99113600000000002</v>
       </c>
       <c r="F81" s="2">
-        <v>0.99113600000000002</v>
-      </c>
-      <c r="G81" s="2">
         <v>-6.4700000000000001E-4</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6">
       <c r="A82" s="2">
         <v>16</v>
       </c>
@@ -2358,16 +2120,13 @@
         <v>0.99176399999999998</v>
       </c>
       <c r="E82" s="2">
-        <v>46</v>
+        <v>0.99505699999999997</v>
       </c>
       <c r="F82" s="2">
-        <v>0.99505699999999997</v>
-      </c>
-      <c r="G82" s="2">
         <v>3.2929999999999999E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6">
       <c r="A83" s="2">
         <v>17</v>
       </c>
@@ -2381,16 +2140,13 @@
         <v>0.99147799999999997</v>
       </c>
       <c r="E83" s="2">
-        <v>129</v>
+        <v>0.98750300000000002</v>
       </c>
       <c r="F83" s="2">
-        <v>0.98750300000000002</v>
-      </c>
-      <c r="G83" s="2">
         <v>-3.9750000000000002E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6">
       <c r="A84" s="2">
         <v>18</v>
       </c>
@@ -2404,16 +2160,13 @@
         <v>0.99141400000000002</v>
       </c>
       <c r="E84" s="2">
-        <v>155</v>
+        <v>0.97568100000000002</v>
       </c>
       <c r="F84" s="2">
-        <v>0.97568100000000002</v>
-      </c>
-      <c r="G84" s="2">
         <v>-1.5734000000000001E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6">
       <c r="A85" s="2">
         <v>19</v>
       </c>
@@ -2427,16 +2180,13 @@
         <v>0.99132299999999995</v>
       </c>
       <c r="E85" s="2">
-        <v>135</v>
+        <v>0.986317</v>
       </c>
       <c r="F85" s="2">
-        <v>0.986317</v>
-      </c>
-      <c r="G85" s="2">
         <v>-5.0070000000000002E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6">
       <c r="A86" s="2">
         <v>20</v>
       </c>
@@ -2450,16 +2200,13 @@
         <v>0.99120600000000003</v>
       </c>
       <c r="E86" s="2">
-        <v>118</v>
+        <v>0.98904999999999998</v>
       </c>
       <c r="F86" s="2">
-        <v>0.98904999999999998</v>
-      </c>
-      <c r="G86" s="2">
         <v>-2.1559999999999999E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6">
       <c r="A87" s="2">
         <v>21</v>
       </c>
@@ -2473,16 +2220,13 @@
         <v>0.99096600000000001</v>
       </c>
       <c r="E87" s="2">
-        <v>48</v>
+        <v>0.99476100000000001</v>
       </c>
       <c r="F87" s="2">
-        <v>0.99476100000000001</v>
-      </c>
-      <c r="G87" s="2">
         <v>3.7950000000000002E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6">
       <c r="A88" s="2">
         <v>22</v>
       </c>
@@ -2496,16 +2240,13 @@
         <v>0.99095299999999997</v>
       </c>
       <c r="E88" s="2">
-        <v>3</v>
+        <v>0.99822299999999997</v>
       </c>
       <c r="F88" s="2">
-        <v>0.99822299999999997</v>
-      </c>
-      <c r="G88" s="2">
         <v>7.2709999999999997E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6">
       <c r="A89" s="2">
         <v>23</v>
       </c>
@@ -2519,16 +2260,13 @@
         <v>0.99094199999999999</v>
       </c>
       <c r="E89" s="2">
-        <v>120</v>
+        <v>0.98895999999999995</v>
       </c>
       <c r="F89" s="2">
-        <v>0.98895999999999995</v>
-      </c>
-      <c r="G89" s="2">
         <v>-1.9819999999999998E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6">
       <c r="A90" s="2">
         <v>24</v>
       </c>
@@ -2542,16 +2280,13 @@
         <v>0.99089899999999997</v>
       </c>
       <c r="E90" s="2">
-        <v>161</v>
+        <v>0.96909900000000004</v>
       </c>
       <c r="F90" s="2">
-        <v>0.96909900000000004</v>
-      </c>
-      <c r="G90" s="2">
         <v>-2.18E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6">
       <c r="A91" s="2">
         <v>25</v>
       </c>
@@ -2565,16 +2300,13 @@
         <v>0.99086600000000002</v>
       </c>
       <c r="E91" s="2">
-        <v>67</v>
+        <v>0.99396600000000002</v>
       </c>
       <c r="F91" s="2">
-        <v>0.99396600000000002</v>
-      </c>
-      <c r="G91" s="2">
         <v>3.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6">
       <c r="A92" s="2">
         <v>26</v>
       </c>
@@ -2588,16 +2320,13 @@
         <v>0.990699</v>
       </c>
       <c r="E92" s="2">
-        <v>91</v>
+        <v>0.99226499999999995</v>
       </c>
       <c r="F92" s="2">
-        <v>0.99226499999999995</v>
-      </c>
-      <c r="G92" s="2">
         <v>1.5659999999999999E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6">
       <c r="A93" s="2">
         <v>27</v>
       </c>
@@ -2611,16 +2340,13 @@
         <v>0.990649</v>
       </c>
       <c r="E93" s="2">
-        <v>88</v>
+        <v>0.99240899999999999</v>
       </c>
       <c r="F93" s="2">
-        <v>0.99240899999999999</v>
-      </c>
-      <c r="G93" s="2">
         <v>1.7600000000000001E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6">
       <c r="A94" s="2">
         <v>28</v>
       </c>
@@ -2634,16 +2360,13 @@
         <v>0.990456</v>
       </c>
       <c r="E94" s="2">
-        <v>163</v>
+        <v>0.96789199999999997</v>
       </c>
       <c r="F94" s="2">
-        <v>0.96789199999999997</v>
-      </c>
-      <c r="G94" s="2">
         <v>-2.2565000000000002E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6">
       <c r="A95" s="2">
         <v>29</v>
       </c>
@@ -2657,16 +2380,13 @@
         <v>0.99044900000000002</v>
       </c>
       <c r="E95" s="2">
-        <v>162</v>
+        <v>0.96837600000000001</v>
       </c>
       <c r="F95" s="2">
-        <v>0.96837600000000001</v>
-      </c>
-      <c r="G95" s="2">
         <v>-2.2072999999999999E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6">
       <c r="A96" s="2">
         <v>30</v>
       </c>
@@ -2680,16 +2400,13 @@
         <v>0.990201</v>
       </c>
       <c r="E96" s="2">
-        <v>116</v>
+        <v>0.98948899999999995</v>
       </c>
       <c r="F96" s="2">
-        <v>0.98948899999999995</v>
-      </c>
-      <c r="G96" s="2">
         <v>-7.1199999999999996E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="A97" s="2">
         <v>31</v>
       </c>
@@ -2703,16 +2420,13 @@
         <v>0.99019000000000001</v>
       </c>
       <c r="E97" s="2">
-        <v>147</v>
+        <v>0.98054200000000002</v>
       </c>
       <c r="F97" s="2">
-        <v>0.98054200000000002</v>
-      </c>
-      <c r="G97" s="2">
         <v>-9.6480000000000003E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6">
       <c r="A98" s="2">
         <v>32</v>
       </c>
@@ -2726,16 +2440,13 @@
         <v>0.99012599999999995</v>
       </c>
       <c r="E98" s="2">
-        <v>59</v>
+        <v>0.99424199999999996</v>
       </c>
       <c r="F98" s="2">
-        <v>0.99424199999999996</v>
-      </c>
-      <c r="G98" s="2">
         <v>4.1159999999999999E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="A99" s="2">
         <v>33</v>
       </c>
@@ -2749,16 +2460,13 @@
         <v>0.99012299999999998</v>
       </c>
       <c r="E99" s="2">
-        <v>125</v>
+        <v>0.98813799999999996</v>
       </c>
       <c r="F99" s="2">
-        <v>0.98813799999999996</v>
-      </c>
-      <c r="G99" s="2">
         <v>-1.9849999999999998E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6">
       <c r="A100" s="2">
         <v>34</v>
       </c>
@@ -2772,16 +2480,13 @@
         <v>0.98999700000000002</v>
       </c>
       <c r="E100" s="2">
-        <v>70</v>
+        <v>0.99368999999999996</v>
       </c>
       <c r="F100" s="2">
-        <v>0.99368999999999996</v>
-      </c>
-      <c r="G100" s="2">
         <v>3.6930000000000001E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6">
       <c r="A101" s="2">
         <v>35</v>
       </c>
@@ -2795,16 +2500,13 @@
         <v>0.98999499999999996</v>
       </c>
       <c r="E101" s="2">
-        <v>121</v>
+        <v>0.98877800000000005</v>
       </c>
       <c r="F101" s="2">
-        <v>0.98877800000000005</v>
-      </c>
-      <c r="G101" s="2">
         <v>-1.217E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6">
       <c r="A102" s="2">
         <v>36</v>
       </c>
@@ -2818,16 +2520,13 @@
         <v>0.98996899999999999</v>
       </c>
       <c r="E102" s="2">
-        <v>158</v>
+        <v>0.97106800000000004</v>
       </c>
       <c r="F102" s="2">
-        <v>0.97106800000000004</v>
-      </c>
-      <c r="G102" s="2">
         <v>-1.89E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6">
       <c r="A103" s="2">
         <v>37</v>
       </c>
@@ -2841,16 +2540,13 @@
         <v>0.98989300000000002</v>
       </c>
       <c r="E103" s="2">
-        <v>136</v>
+        <v>0.985931</v>
       </c>
       <c r="F103" s="2">
-        <v>0.985931</v>
-      </c>
-      <c r="G103" s="2">
         <v>-3.9610000000000001E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="A104" s="2">
         <v>38</v>
       </c>
@@ -2864,16 +2560,13 @@
         <v>0.98973199999999995</v>
       </c>
       <c r="E104" s="2">
-        <v>28</v>
+        <v>0.99574200000000002</v>
       </c>
       <c r="F104" s="2">
-        <v>0.99574200000000002</v>
-      </c>
-      <c r="G104" s="2">
         <v>6.0109999999999999E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6">
       <c r="A105" s="2">
         <v>39</v>
       </c>
@@ -2887,16 +2580,13 @@
         <v>0.98949100000000001</v>
       </c>
       <c r="E105" s="2">
-        <v>37</v>
+        <v>0.99548599999999998</v>
       </c>
       <c r="F105" s="2">
-        <v>0.99548599999999998</v>
-      </c>
-      <c r="G105" s="2">
         <v>5.9950000000000003E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6">
       <c r="A106" s="3">
         <v>40</v>
       </c>
@@ -2910,16 +2600,13 @@
         <v>0.98930399999999996</v>
       </c>
       <c r="E106" s="3">
-        <v>181</v>
-      </c>
-      <c r="F106" s="3">
         <v>0.36402899999999999</v>
       </c>
-      <c r="G106" s="2">
+      <c r="F106" s="2">
         <v>-0.62527500000000003</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6">
       <c r="A107" s="2">
         <v>41</v>
       </c>
@@ -2933,16 +2620,13 @@
         <v>0.98927399999999999</v>
       </c>
       <c r="E107" s="2">
-        <v>114</v>
+        <v>0.98959699999999995</v>
       </c>
       <c r="F107" s="2">
-        <v>0.98959699999999995</v>
-      </c>
-      <c r="G107" s="2">
         <v>3.2400000000000001E-4</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6">
       <c r="A108" s="2">
         <v>42</v>
       </c>
@@ -2956,16 +2640,13 @@
         <v>0.98919500000000005</v>
       </c>
       <c r="E108" s="2">
-        <v>130</v>
+        <v>0.98736199999999996</v>
       </c>
       <c r="F108" s="2">
-        <v>0.98736199999999996</v>
-      </c>
-      <c r="G108" s="2">
         <v>-1.8339999999999999E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6">
       <c r="A109" s="2">
         <v>43</v>
       </c>
@@ -2979,16 +2660,13 @@
         <v>0.98918300000000003</v>
       </c>
       <c r="E109" s="2">
-        <v>84</v>
+        <v>0.99302699999999999</v>
       </c>
       <c r="F109" s="2">
-        <v>0.99302699999999999</v>
-      </c>
-      <c r="G109" s="2">
         <v>3.8440000000000002E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6">
       <c r="A110" s="2">
         <v>44</v>
       </c>
@@ -3002,16 +2680,13 @@
         <v>0.98915600000000004</v>
       </c>
       <c r="E110" s="2">
-        <v>138</v>
+        <v>0.98544799999999999</v>
       </c>
       <c r="F110" s="2">
-        <v>0.98544799999999999</v>
-      </c>
-      <c r="G110" s="2">
         <v>-3.7079999999999999E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6">
       <c r="A111" s="2">
         <v>45</v>
       </c>
@@ -3025,39 +2700,33 @@
         <v>0.989097</v>
       </c>
       <c r="E111" s="2">
-        <v>124</v>
+        <v>0.98850899999999997</v>
       </c>
       <c r="F111" s="2">
-        <v>0.98850899999999997</v>
-      </c>
-      <c r="G111" s="2">
         <v>-5.8799999999999998E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" s="2">
+    <row r="112" spans="1:6">
+      <c r="A112" s="4">
         <v>46</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="4">
         <v>19782535</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112" s="4">
         <v>111</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="4">
         <v>0.98906700000000003</v>
       </c>
-      <c r="E112" s="2">
-        <v>177</v>
+      <c r="E112" s="4">
+        <v>0.881525</v>
       </c>
       <c r="F112" s="2">
-        <v>0.881525</v>
-      </c>
-      <c r="G112" s="2">
         <v>-0.107542</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="A113" s="2">
         <v>47</v>
       </c>
@@ -3071,16 +2740,13 @@
         <v>0.98902199999999996</v>
       </c>
       <c r="E113" s="2">
-        <v>132</v>
+        <v>0.98662300000000003</v>
       </c>
       <c r="F113" s="2">
-        <v>0.98662300000000003</v>
-      </c>
-      <c r="G113" s="2">
         <v>-2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="A114" s="2">
         <v>48</v>
       </c>
@@ -3094,16 +2760,13 @@
         <v>0.98894800000000005</v>
       </c>
       <c r="E114" s="2">
-        <v>153</v>
+        <v>0.97909000000000002</v>
       </c>
       <c r="F114" s="2">
-        <v>0.97909000000000002</v>
-      </c>
-      <c r="G114" s="2">
         <v>-9.8580000000000004E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="A115" s="2">
         <v>49</v>
       </c>
@@ -3117,16 +2780,13 @@
         <v>0.988931</v>
       </c>
       <c r="E115" s="2">
-        <v>140</v>
+        <v>0.985066</v>
       </c>
       <c r="F115" s="2">
-        <v>0.985066</v>
-      </c>
-      <c r="G115" s="2">
         <v>-3.8649999999999999E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6">
       <c r="A116" s="2">
         <v>50</v>
       </c>
@@ -3140,16 +2800,13 @@
         <v>0.98891300000000004</v>
       </c>
       <c r="E116" s="2">
-        <v>110</v>
+        <v>0.99027399999999999</v>
       </c>
       <c r="F116" s="2">
-        <v>0.99027399999999999</v>
-      </c>
-      <c r="G116" s="2">
         <v>1.361E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="A117" s="2">
         <v>51</v>
       </c>
@@ -3163,16 +2820,13 @@
         <v>0.98891099999999998</v>
       </c>
       <c r="E117" s="2">
-        <v>111</v>
+        <v>0.99009000000000003</v>
       </c>
       <c r="F117" s="2">
-        <v>0.99009000000000003</v>
-      </c>
-      <c r="G117" s="2">
         <v>1.178E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6">
       <c r="A118" s="2">
         <v>52</v>
       </c>
@@ -3186,16 +2840,13 @@
         <v>0.98883200000000004</v>
       </c>
       <c r="E118" s="2">
-        <v>29</v>
+        <v>0.99568100000000004</v>
       </c>
       <c r="F118" s="2">
-        <v>0.99568100000000004</v>
-      </c>
-      <c r="G118" s="2">
         <v>6.8490000000000001E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6">
       <c r="A119" s="2">
         <v>53</v>
       </c>
@@ -3209,16 +2860,13 @@
         <v>0.98881699999999995</v>
       </c>
       <c r="E119" s="2">
-        <v>104</v>
+        <v>0.99100999999999995</v>
       </c>
       <c r="F119" s="2">
-        <v>0.99100999999999995</v>
-      </c>
-      <c r="G119" s="2">
         <v>2.1930000000000001E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6">
       <c r="A120" s="2">
         <v>54</v>
       </c>
@@ -3232,16 +2880,13 @@
         <v>0.98874300000000004</v>
       </c>
       <c r="E120" s="2">
-        <v>94</v>
+        <v>0.992197</v>
       </c>
       <c r="F120" s="2">
-        <v>0.992197</v>
-      </c>
-      <c r="G120" s="2">
         <v>3.454E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6">
       <c r="A121" s="2">
         <v>55</v>
       </c>
@@ -3255,16 +2900,13 @@
         <v>0.98871399999999998</v>
       </c>
       <c r="E121" s="2">
-        <v>65</v>
+        <v>0.99411300000000002</v>
       </c>
       <c r="F121" s="2">
-        <v>0.99411300000000002</v>
-      </c>
-      <c r="G121" s="2">
         <v>5.3990000000000002E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6">
       <c r="A122" s="2">
         <v>56</v>
       </c>
@@ -3278,16 +2920,13 @@
         <v>0.98866600000000004</v>
       </c>
       <c r="E122" s="2">
-        <v>122</v>
+        <v>0.988626</v>
       </c>
       <c r="F122" s="2">
-        <v>0.988626</v>
-      </c>
-      <c r="G122" s="2">
         <v>-4.1E-5</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
       <c r="A123" s="2">
         <v>57</v>
       </c>
@@ -3301,16 +2940,13 @@
         <v>0.98862700000000003</v>
       </c>
       <c r="E123" s="2">
-        <v>76</v>
+        <v>0.99344299999999996</v>
       </c>
       <c r="F123" s="2">
-        <v>0.99344299999999996</v>
-      </c>
-      <c r="G123" s="2">
         <v>4.816E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6">
       <c r="A124" s="2">
         <v>58</v>
       </c>
@@ -3324,16 +2960,13 @@
         <v>0.98845700000000003</v>
       </c>
       <c r="E124" s="2">
-        <v>146</v>
+        <v>0.98243199999999997</v>
       </c>
       <c r="F124" s="2">
-        <v>0.98243199999999997</v>
-      </c>
-      <c r="G124" s="2">
         <v>-6.025E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6">
       <c r="A125" s="2">
         <v>59</v>
       </c>
@@ -3347,16 +2980,13 @@
         <v>0.988367</v>
       </c>
       <c r="E125" s="2">
-        <v>51</v>
+        <v>0.99466200000000005</v>
       </c>
       <c r="F125" s="2">
-        <v>0.99466200000000005</v>
-      </c>
-      <c r="G125" s="2">
         <v>6.2960000000000004E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6">
       <c r="A126" s="2">
         <v>60</v>
       </c>
@@ -3370,16 +3000,13 @@
         <v>0.98827500000000001</v>
       </c>
       <c r="E126" s="2">
-        <v>168</v>
+        <v>0.951179</v>
       </c>
       <c r="F126" s="2">
-        <v>0.951179</v>
-      </c>
-      <c r="G126" s="2">
         <v>-3.7095999999999997E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="A127" s="2">
         <v>61</v>
       </c>
@@ -3393,16 +3020,13 @@
         <v>0.988263</v>
       </c>
       <c r="E127" s="2">
-        <v>170</v>
+        <v>0.94070600000000004</v>
       </c>
       <c r="F127" s="2">
-        <v>0.94070600000000004</v>
-      </c>
-      <c r="G127" s="2">
         <v>-4.7557000000000002E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="A128" s="2">
         <v>62</v>
       </c>
@@ -3416,16 +3040,13 @@
         <v>0.98814999999999997</v>
       </c>
       <c r="E128" s="2">
-        <v>54</v>
+        <v>0.994529</v>
       </c>
       <c r="F128" s="2">
-        <v>0.994529</v>
-      </c>
-      <c r="G128" s="2">
         <v>6.3790000000000001E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6">
       <c r="A129" s="2">
         <v>63</v>
       </c>
@@ -3439,16 +3060,13 @@
         <v>0.98809599999999997</v>
       </c>
       <c r="E129" s="2">
-        <v>137</v>
+        <v>0.98569099999999998</v>
       </c>
       <c r="F129" s="2">
-        <v>0.98569099999999998</v>
-      </c>
-      <c r="G129" s="2">
         <v>-2.405E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="A130" s="2">
         <v>64</v>
       </c>
@@ -3462,16 +3080,13 @@
         <v>0.98807299999999998</v>
       </c>
       <c r="E130" s="2">
-        <v>58</v>
+        <v>0.99438400000000005</v>
       </c>
       <c r="F130" s="2">
-        <v>0.99438400000000005</v>
-      </c>
-      <c r="G130" s="2">
         <v>6.3109999999999998E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6">
       <c r="A131" s="2">
         <v>65</v>
       </c>
@@ -3485,16 +3100,13 @@
         <v>0.9879</v>
       </c>
       <c r="E131" s="2">
-        <v>80</v>
+        <v>0.99317</v>
       </c>
       <c r="F131" s="2">
-        <v>0.99317</v>
-      </c>
-      <c r="G131" s="2">
         <v>5.2709999999999996E-3</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="A132" s="2">
         <v>66</v>
       </c>
@@ -3508,16 +3120,13 @@
         <v>0.98785400000000001</v>
       </c>
       <c r="E132" s="2">
-        <v>126</v>
+        <v>0.98807299999999998</v>
       </c>
       <c r="F132" s="2">
-        <v>0.98807299999999998</v>
-      </c>
-      <c r="G132" s="2">
         <v>2.1900000000000001E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="A133" s="3">
         <v>67</v>
       </c>
@@ -3531,16 +3140,13 @@
         <v>0.987842</v>
       </c>
       <c r="E133" s="3">
-        <v>182</v>
-      </c>
-      <c r="F133" s="3">
         <v>0.35622100000000001</v>
       </c>
-      <c r="G133" s="2">
+      <c r="F133" s="2">
         <v>-0.63162099999999999</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="A134" s="2">
         <v>68</v>
       </c>
@@ -3554,16 +3160,13 @@
         <v>0.98775199999999996</v>
       </c>
       <c r="E134" s="2">
-        <v>68</v>
+        <v>0.993815</v>
       </c>
       <c r="F134" s="2">
-        <v>0.993815</v>
-      </c>
-      <c r="G134" s="2">
         <v>6.0629999999999998E-3</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6">
       <c r="A135" s="2">
         <v>69</v>
       </c>
@@ -3577,16 +3180,13 @@
         <v>0.98771299999999995</v>
       </c>
       <c r="E135" s="2">
-        <v>21</v>
+        <v>0.99629900000000005</v>
       </c>
       <c r="F135" s="2">
-        <v>0.99629900000000005</v>
-      </c>
-      <c r="G135" s="2">
         <v>8.5859999999999999E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="A136" s="2">
         <v>70</v>
       </c>
@@ -3600,16 +3200,13 @@
         <v>0.98767199999999999</v>
       </c>
       <c r="E136" s="2">
-        <v>154</v>
+        <v>0.977661</v>
       </c>
       <c r="F136" s="2">
-        <v>0.977661</v>
-      </c>
-      <c r="G136" s="2">
         <v>-1.0011000000000001E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6">
       <c r="A137" s="2">
         <v>71</v>
       </c>
@@ -3623,16 +3220,13 @@
         <v>0.98750800000000005</v>
       </c>
       <c r="E137" s="2">
-        <v>31</v>
+        <v>0.99563900000000005</v>
       </c>
       <c r="F137" s="2">
-        <v>0.99563900000000005</v>
-      </c>
-      <c r="G137" s="2">
         <v>8.1309999999999993E-3</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6">
       <c r="A138" s="2">
         <v>72</v>
       </c>
@@ -3646,16 +3240,13 @@
         <v>0.98745400000000005</v>
       </c>
       <c r="E138" s="2">
-        <v>60</v>
+        <v>0.99419800000000003</v>
       </c>
       <c r="F138" s="2">
-        <v>0.99419800000000003</v>
-      </c>
-      <c r="G138" s="2">
         <v>6.744E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6">
       <c r="A139" s="2">
         <v>73</v>
       </c>
@@ -3669,16 +3260,13 @@
         <v>0.98738800000000004</v>
       </c>
       <c r="E139" s="2">
-        <v>85</v>
+        <v>0.99291799999999997</v>
       </c>
       <c r="F139" s="2">
-        <v>0.99291799999999997</v>
-      </c>
-      <c r="G139" s="2">
         <v>5.5300000000000002E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="A140" s="2">
         <v>74</v>
       </c>
@@ -3692,16 +3280,13 @@
         <v>0.98733899999999997</v>
       </c>
       <c r="E140" s="2">
-        <v>157</v>
+        <v>0.97150700000000001</v>
       </c>
       <c r="F140" s="2">
-        <v>0.97150700000000001</v>
-      </c>
-      <c r="G140" s="2">
         <v>-1.5831999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6">
       <c r="A141" s="2">
         <v>75</v>
       </c>
@@ -3715,16 +3300,13 @@
         <v>0.98722699999999997</v>
       </c>
       <c r="E141" s="2">
-        <v>144</v>
+        <v>0.983429</v>
       </c>
       <c r="F141" s="2">
-        <v>0.983429</v>
-      </c>
-      <c r="G141" s="2">
         <v>-3.7989999999999999E-3</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6">
       <c r="A142" s="2">
         <v>76</v>
       </c>
@@ -3738,16 +3320,13 @@
         <v>0.98717699999999997</v>
       </c>
       <c r="E142" s="2">
-        <v>172</v>
+        <v>0.922149</v>
       </c>
       <c r="F142" s="2">
-        <v>0.922149</v>
-      </c>
-      <c r="G142" s="2">
         <v>-6.5028000000000002E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6">
       <c r="A143" s="2">
         <v>77</v>
       </c>
@@ -3761,16 +3340,13 @@
         <v>0.98714599999999997</v>
       </c>
       <c r="E143" s="2">
-        <v>95</v>
+        <v>0.99199099999999996</v>
       </c>
       <c r="F143" s="2">
-        <v>0.99199099999999996</v>
-      </c>
-      <c r="G143" s="2">
         <v>4.8450000000000003E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6">
       <c r="A144" s="2">
         <v>78</v>
       </c>
@@ -3784,16 +3360,13 @@
         <v>0.98713200000000001</v>
       </c>
       <c r="E144" s="2">
-        <v>142</v>
+        <v>0.98491300000000004</v>
       </c>
       <c r="F144" s="2">
-        <v>0.98491300000000004</v>
-      </c>
-      <c r="G144" s="2">
         <v>-2.2190000000000001E-3</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6">
       <c r="A145" s="2">
         <v>79</v>
       </c>
@@ -3807,16 +3380,13 @@
         <v>0.98706099999999997</v>
       </c>
       <c r="E145" s="2">
-        <v>33</v>
+        <v>0.99562300000000004</v>
       </c>
       <c r="F145" s="2">
-        <v>0.99562300000000004</v>
-      </c>
-      <c r="G145" s="2">
         <v>8.5609999999999992E-3</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6">
       <c r="A146" s="2">
         <v>80</v>
       </c>
@@ -3830,16 +3400,13 @@
         <v>0.98705900000000002</v>
       </c>
       <c r="E146" s="2">
-        <v>71</v>
+        <v>0.99367000000000005</v>
       </c>
       <c r="F146" s="2">
-        <v>0.99367000000000005</v>
-      </c>
-      <c r="G146" s="2">
         <v>6.6119999999999998E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6">
       <c r="A147" s="2">
         <v>81</v>
       </c>
@@ -3853,16 +3420,13 @@
         <v>0.98678600000000005</v>
       </c>
       <c r="E147" s="2">
-        <v>169</v>
+        <v>0.95098000000000005</v>
       </c>
       <c r="F147" s="2">
-        <v>0.95098000000000005</v>
-      </c>
-      <c r="G147" s="2">
         <v>-3.5805999999999998E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6">
       <c r="A148" s="2">
         <v>82</v>
       </c>
@@ -3876,16 +3440,13 @@
         <v>0.98675100000000004</v>
       </c>
       <c r="E148" s="2">
-        <v>123</v>
+        <v>0.98851199999999995</v>
       </c>
       <c r="F148" s="2">
-        <v>0.98851199999999995</v>
-      </c>
-      <c r="G148" s="2">
         <v>1.761E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6">
       <c r="A149" s="2">
         <v>83</v>
       </c>
@@ -3899,16 +3460,13 @@
         <v>0.98661100000000002</v>
       </c>
       <c r="E149" s="2">
-        <v>112</v>
+        <v>0.99007000000000001</v>
       </c>
       <c r="F149" s="2">
-        <v>0.99007000000000001</v>
-      </c>
-      <c r="G149" s="2">
         <v>3.4589999999999998E-3</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6">
       <c r="A150" s="2">
         <v>84</v>
       </c>
@@ -3922,16 +3480,13 @@
         <v>0.98650499999999997</v>
       </c>
       <c r="E150" s="2">
-        <v>173</v>
+        <v>0.89345699999999995</v>
       </c>
       <c r="F150" s="2">
-        <v>0.89345699999999995</v>
-      </c>
-      <c r="G150" s="2">
         <v>-9.3048000000000006E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6">
       <c r="A151" s="2">
         <v>85</v>
       </c>
@@ -3945,16 +3500,13 @@
         <v>0.98646100000000003</v>
       </c>
       <c r="E151" s="2">
-        <v>174</v>
+        <v>0.89091699999999996</v>
       </c>
       <c r="F151" s="2">
-        <v>0.89091699999999996</v>
-      </c>
-      <c r="G151" s="2">
         <v>-9.5544000000000004E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6">
       <c r="A152" s="2">
         <v>86</v>
       </c>
@@ -3968,16 +3520,13 @@
         <v>0.98633700000000002</v>
       </c>
       <c r="E152" s="2">
-        <v>117</v>
+        <v>0.98909800000000003</v>
       </c>
       <c r="F152" s="2">
-        <v>0.98909800000000003</v>
-      </c>
-      <c r="G152" s="2">
         <v>2.7620000000000001E-3</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6">
       <c r="A153" s="3">
         <v>87</v>
       </c>
@@ -3991,16 +3540,13 @@
         <v>0.98614599999999997</v>
       </c>
       <c r="E153" s="3">
-        <v>184</v>
-      </c>
-      <c r="F153" s="3">
         <v>0.23907700000000001</v>
       </c>
-      <c r="G153" s="2">
+      <c r="F153" s="2">
         <v>-0.74706899999999998</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6">
       <c r="A154" s="2">
         <v>88</v>
       </c>
@@ -4014,16 +3560,13 @@
         <v>0.98614000000000002</v>
       </c>
       <c r="E154" s="2">
-        <v>98</v>
+        <v>0.99134599999999995</v>
       </c>
       <c r="F154" s="2">
-        <v>0.99134599999999995</v>
-      </c>
-      <c r="G154" s="2">
         <v>5.2059999999999997E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6">
       <c r="A155" s="2">
         <v>89</v>
       </c>
@@ -4037,16 +3580,13 @@
         <v>0.98600600000000005</v>
       </c>
       <c r="E155" s="2">
-        <v>100</v>
+        <v>0.99116899999999997</v>
       </c>
       <c r="F155" s="2">
-        <v>0.99116899999999997</v>
-      </c>
-      <c r="G155" s="2">
         <v>5.1630000000000001E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6">
       <c r="A156" s="2">
         <v>90</v>
       </c>
@@ -4060,16 +3600,13 @@
         <v>0.98596600000000001</v>
       </c>
       <c r="E156" s="2">
-        <v>160</v>
+        <v>0.96926500000000004</v>
       </c>
       <c r="F156" s="2">
-        <v>0.96926500000000004</v>
-      </c>
-      <c r="G156" s="2">
         <v>-1.6701000000000001E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6">
       <c r="A157" s="2">
         <v>91</v>
       </c>
@@ -4083,16 +3620,13 @@
         <v>0.985958</v>
       </c>
       <c r="E157" s="2">
-        <v>151</v>
+        <v>0.97967000000000004</v>
       </c>
       <c r="F157" s="2">
-        <v>0.97967000000000004</v>
-      </c>
-      <c r="G157" s="2">
         <v>-6.2880000000000002E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6">
       <c r="A158" s="2">
         <v>92</v>
       </c>
@@ -4106,16 +3640,13 @@
         <v>0.98579000000000006</v>
       </c>
       <c r="E158" s="2">
-        <v>131</v>
+        <v>0.986676</v>
       </c>
       <c r="F158" s="2">
-        <v>0.986676</v>
-      </c>
-      <c r="G158" s="2">
         <v>8.8599999999999996E-4</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6">
       <c r="A159" s="2">
         <v>93</v>
       </c>
@@ -4129,16 +3660,13 @@
         <v>0.98570500000000005</v>
       </c>
       <c r="E159" s="2">
-        <v>164</v>
+        <v>0.96654600000000002</v>
       </c>
       <c r="F159" s="2">
-        <v>0.96654600000000002</v>
-      </c>
-      <c r="G159" s="2">
         <v>-1.9158000000000001E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6">
       <c r="A160" s="2">
         <v>94</v>
       </c>
@@ -4152,16 +3680,13 @@
         <v>0.98567499999999997</v>
       </c>
       <c r="E160" s="2">
-        <v>152</v>
+        <v>0.97939399999999999</v>
       </c>
       <c r="F160" s="2">
-        <v>0.97939399999999999</v>
-      </c>
-      <c r="G160" s="2">
         <v>-6.2810000000000001E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6">
       <c r="A161" s="2">
         <v>95</v>
       </c>
@@ -4175,16 +3700,13 @@
         <v>0.98562099999999997</v>
       </c>
       <c r="E161" s="2">
-        <v>149</v>
+        <v>0.98036100000000004</v>
       </c>
       <c r="F161" s="2">
-        <v>0.98036100000000004</v>
-      </c>
-      <c r="G161" s="2">
         <v>-5.2599999999999999E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6">
       <c r="A162" s="2">
         <v>96</v>
       </c>
@@ -4198,16 +3720,13 @@
         <v>0.98536999999999997</v>
       </c>
       <c r="E162" s="2">
-        <v>66</v>
+        <v>0.99407000000000001</v>
       </c>
       <c r="F162" s="2">
-        <v>0.99407000000000001</v>
-      </c>
-      <c r="G162" s="2">
         <v>8.6990000000000001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6">
       <c r="A163" s="2">
         <v>97</v>
       </c>
@@ -4221,16 +3740,13 @@
         <v>0.98532500000000001</v>
       </c>
       <c r="E163" s="2">
-        <v>119</v>
+        <v>0.98904800000000004</v>
       </c>
       <c r="F163" s="2">
-        <v>0.98904800000000004</v>
-      </c>
-      <c r="G163" s="2">
         <v>3.7230000000000002E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6">
       <c r="A164" s="2">
         <v>98</v>
       </c>
@@ -4244,16 +3760,13 @@
         <v>0.98526000000000002</v>
       </c>
       <c r="E164" s="2">
-        <v>143</v>
+        <v>0.98459099999999999</v>
       </c>
       <c r="F164" s="2">
-        <v>0.98459099999999999</v>
-      </c>
-      <c r="G164" s="2">
         <v>-6.69E-4</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6">
       <c r="A165" s="2">
         <v>99</v>
       </c>
@@ -4267,16 +3780,13 @@
         <v>0.98520600000000003</v>
       </c>
       <c r="E165" s="2">
-        <v>139</v>
+        <v>0.98523099999999997</v>
       </c>
       <c r="F165" s="2">
-        <v>0.98523099999999997</v>
-      </c>
-      <c r="G165" s="2">
         <v>2.5000000000000001E-5</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6">
       <c r="A166" s="2">
         <v>100</v>
       </c>
@@ -4290,16 +3800,13 @@
         <v>0.98511199999999999</v>
       </c>
       <c r="E166" s="2">
-        <v>167</v>
+        <v>0.95533999999999997</v>
       </c>
       <c r="F166" s="2">
-        <v>0.95533999999999997</v>
-      </c>
-      <c r="G166" s="2">
         <v>-2.9772E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6">
       <c r="A167" s="2">
         <v>101</v>
       </c>
@@ -4313,16 +3820,13 @@
         <v>0.98503399999999997</v>
       </c>
       <c r="E167" s="2">
-        <v>44</v>
+        <v>0.99522200000000005</v>
       </c>
       <c r="F167" s="2">
-        <v>0.99522200000000005</v>
-      </c>
-      <c r="G167" s="2">
         <v>1.0187E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6">
       <c r="A168" s="2">
         <v>102</v>
       </c>
@@ -4336,16 +3840,13 @@
         <v>0.98489700000000002</v>
       </c>
       <c r="E168" s="2">
-        <v>108</v>
+        <v>0.99060199999999998</v>
       </c>
       <c r="F168" s="2">
-        <v>0.99060199999999998</v>
-      </c>
-      <c r="G168" s="2">
         <v>5.705E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6">
       <c r="A169" s="2">
         <v>103</v>
       </c>
@@ -4359,16 +3860,13 @@
         <v>0.98487199999999997</v>
       </c>
       <c r="E169" s="2">
-        <v>171</v>
+        <v>0.92366899999999996</v>
       </c>
       <c r="F169" s="2">
-        <v>0.92366899999999996</v>
-      </c>
-      <c r="G169" s="2">
         <v>-6.1203E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6">
       <c r="A170" s="2">
         <v>104</v>
       </c>
@@ -4382,16 +3880,13 @@
         <v>0.98476900000000001</v>
       </c>
       <c r="E170" s="2">
-        <v>166</v>
+        <v>0.95809500000000003</v>
       </c>
       <c r="F170" s="2">
-        <v>0.95809500000000003</v>
-      </c>
-      <c r="G170" s="2">
         <v>-2.6675000000000001E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6">
       <c r="A171" s="2">
         <v>105</v>
       </c>
@@ -4405,16 +3900,13 @@
         <v>0.98475900000000005</v>
       </c>
       <c r="E171" s="2">
-        <v>72</v>
+        <v>0.99365599999999998</v>
       </c>
       <c r="F171" s="2">
-        <v>0.99365599999999998</v>
-      </c>
-      <c r="G171" s="2">
         <v>8.8970000000000004E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6">
       <c r="A172" s="3">
         <v>106</v>
       </c>
@@ -4428,16 +3920,13 @@
         <v>0.98466500000000001</v>
       </c>
       <c r="E172" s="3">
-        <v>180</v>
-      </c>
-      <c r="F172" s="3">
         <v>0.39042199999999999</v>
       </c>
-      <c r="G172" s="2">
+      <c r="F172" s="2">
         <v>-0.59424299999999997</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6">
       <c r="A173" s="2">
         <v>107</v>
       </c>
@@ -4451,16 +3940,13 @@
         <v>0.98451500000000003</v>
       </c>
       <c r="E173" s="2">
-        <v>103</v>
+        <v>0.99108099999999999</v>
       </c>
       <c r="F173" s="2">
-        <v>0.99108099999999999</v>
-      </c>
-      <c r="G173" s="2">
         <v>6.5669999999999999E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6">
       <c r="A174" s="2">
         <v>108</v>
       </c>
@@ -4474,16 +3960,13 @@
         <v>0.98451299999999997</v>
       </c>
       <c r="E174" s="2">
-        <v>106</v>
+        <v>0.99086799999999997</v>
       </c>
       <c r="F174" s="2">
-        <v>0.99086799999999997</v>
-      </c>
-      <c r="G174" s="2">
         <v>6.3550000000000004E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6">
       <c r="A175" s="2">
         <v>109</v>
       </c>
@@ -4497,16 +3980,13 @@
         <v>0.98449600000000004</v>
       </c>
       <c r="E175" s="2">
-        <v>127</v>
+        <v>0.98798600000000003</v>
       </c>
       <c r="F175" s="2">
-        <v>0.98798600000000003</v>
-      </c>
-      <c r="G175" s="2">
         <v>3.49E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6">
       <c r="A176" s="2">
         <v>110</v>
       </c>
@@ -4520,16 +4000,13 @@
         <v>0.98441500000000004</v>
       </c>
       <c r="E176" s="2">
-        <v>133</v>
+        <v>0.98659200000000002</v>
       </c>
       <c r="F176" s="2">
-        <v>0.98659200000000002</v>
-      </c>
-      <c r="G176" s="2">
         <v>2.1770000000000001E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6">
       <c r="A177" s="2">
         <v>111</v>
       </c>
@@ -4543,16 +4020,13 @@
         <v>0.98430399999999996</v>
       </c>
       <c r="E177" s="2">
-        <v>115</v>
+        <v>0.98958599999999997</v>
       </c>
       <c r="F177" s="2">
-        <v>0.98958599999999997</v>
-      </c>
-      <c r="G177" s="2">
         <v>5.2810000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6">
       <c r="A178" s="2">
         <v>112</v>
       </c>
@@ -4566,16 +4040,13 @@
         <v>0.98427600000000004</v>
       </c>
       <c r="E178" s="2">
-        <v>175</v>
+        <v>0.88665899999999997</v>
       </c>
       <c r="F178" s="2">
-        <v>0.88665899999999997</v>
-      </c>
-      <c r="G178" s="2">
         <v>-9.7616999999999995E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6">
       <c r="A179" s="2">
         <v>113</v>
       </c>
@@ -4589,16 +4060,13 @@
         <v>0.98427200000000004</v>
       </c>
       <c r="E179" s="2">
-        <v>34</v>
+        <v>0.99553199999999997</v>
       </c>
       <c r="F179" s="2">
-        <v>0.99553199999999997</v>
-      </c>
-      <c r="G179" s="2">
         <v>1.1259999999999999E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6">
       <c r="A180" s="2">
         <v>114</v>
       </c>
@@ -4612,16 +4080,13 @@
         <v>0.98424900000000004</v>
       </c>
       <c r="E180" s="2">
-        <v>148</v>
+        <v>0.98053999999999997</v>
       </c>
       <c r="F180" s="2">
-        <v>0.98053999999999997</v>
-      </c>
-      <c r="G180" s="2">
         <v>-3.7100000000000002E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6">
       <c r="A181" s="2">
         <v>115</v>
       </c>
@@ -4635,16 +4100,13 @@
         <v>0.98423000000000005</v>
       </c>
       <c r="E181" s="2">
-        <v>134</v>
+        <v>0.98650000000000004</v>
       </c>
       <c r="F181" s="2">
-        <v>0.98650000000000004</v>
-      </c>
-      <c r="G181" s="2">
         <v>2.2690000000000002E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6">
       <c r="A182" s="2">
         <v>116</v>
       </c>
@@ -4658,16 +4120,13 @@
         <v>0.98408600000000002</v>
       </c>
       <c r="E182" s="2">
-        <v>159</v>
+        <v>0.97086499999999998</v>
       </c>
       <c r="F182" s="2">
-        <v>0.97086499999999998</v>
-      </c>
-      <c r="G182" s="2">
         <v>-1.3221E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6">
       <c r="A183" s="2">
         <v>117</v>
       </c>
@@ -4681,16 +4140,13 @@
         <v>0.98404800000000003</v>
       </c>
       <c r="E183" s="2">
-        <v>156</v>
+        <v>0.97486300000000004</v>
       </c>
       <c r="F183" s="2">
-        <v>0.97486300000000004</v>
-      </c>
-      <c r="G183" s="2">
         <v>-9.1850000000000005E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6">
       <c r="A184" s="2">
         <v>118</v>
       </c>
@@ -4704,16 +4160,13 @@
         <v>0.98400500000000002</v>
       </c>
       <c r="E184" s="2">
-        <v>113</v>
+        <v>0.98983500000000002</v>
       </c>
       <c r="F184" s="2">
-        <v>0.98983500000000002</v>
-      </c>
-      <c r="G184" s="2">
         <v>5.829E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6">
       <c r="A185" s="2">
         <v>119</v>
       </c>
@@ -4727,17 +4180,14 @@
         <v>0.98396899999999998</v>
       </c>
       <c r="E185" s="2">
-        <v>165</v>
+        <v>0.96455199999999996</v>
       </c>
       <c r="F185" s="2">
-        <v>0.96455199999999996</v>
-      </c>
-      <c r="G185" s="2">
         <v>-1.9415999999999999E-2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G1:G185">
+  <conditionalFormatting sqref="F1:F185">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
